--- a/education_surveys/006_global_economic_empowerment_survey--education_surveys.xlsx
+++ b/education_surveys/006_global_economic_empowerment_survey--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'government'}</t>
+          <t>government</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Government'}</t>
+          <t>Government</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'private_sector'}</t>
+          <t>private_sector</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Private Sector'}</t>
+          <t>Private Sector</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'self_employment'}</t>
+          <t>self_employment</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Self Employment'}</t>
+          <t>Self Employment</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'bank'}</t>
+          <t>bank</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Bank'}</t>
+          <t>Bank</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'credit_union'}</t>
+          <t>credit_union</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Credit Union'}</t>
+          <t>Credit Union</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'microfinance_institution'}</t>
+          <t>microfinance_institution</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Microfinance Institution'}</t>
+          <t>Microfinance Institution</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'included'}</t>
+          <t>included</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Included'}</t>
+          <t>Included</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'not_included'}</t>
+          <t>not_included</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Not Included'}</t>
+          <t>Not Included</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'prefer_not_to_say'}</t>
+          <t>prefer_not_to_say</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Prefer not to say'}</t>
+          <t>Prefer not to say</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'region_1'}</t>
+          <t>region_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Region 1'}</t>
+          <t>Region 1</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'region_2'}</t>
+          <t>region_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Region 2'}</t>
+          <t>Region 2</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'region_3'}</t>
+          <t>region_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Region 3'}</t>
+          <t>Region 3</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'High School'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'college/university'}</t>
+          <t>college/university</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'College/University'}</t>
+          <t>College/University</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'married'}</t>
+          <t>married</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Married'}</t>
+          <t>Married</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'less_than_5'}</t>
+          <t>less_than_5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Less than 5'}</t>
+          <t>Less than 5</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'5_or_more'}</t>
+          <t>5_or_more</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': '5 or more'}</t>
+          <t>5 or more</t>
         </is>
       </c>
     </row>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'formal'}</t>
+          <t>formal</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'Formal'}</t>
+          <t>Formal</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'informal'}</t>
+          <t>informal</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'Informal'}</t>
+          <t>Informal</t>
         </is>
       </c>
     </row>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1479,12 +1479,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
